--- a/results/表4_水分浓度.xlsx
+++ b/results/表4_水分浓度.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -639,7 +639,7 @@
     <row r="1" ht="14.1" customHeight="1" s="4">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>时间\到药材中心的距离</t>
+          <t>时间/h\到药材中心的距离/cm</t>
         </is>
       </c>
       <c r="B1" s="1" t="n">
@@ -660,122 +660,122 @@
     </row>
     <row r="2" ht="14.1" customHeight="1" s="4">
       <c r="A2" s="1" t="n">
-        <v>1800</v>
+        <v>0.5</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>2.54993</v>
+        <v>2.5499</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>2.54888</v>
+        <v>2.5489</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>2.52553</v>
+        <v>2.5255</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2.32566</v>
+        <v>2.3257</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1.66021</v>
+        <v>1.6486</v>
       </c>
     </row>
     <row r="3" ht="14.1" customHeight="1" s="4">
       <c r="A3" s="1" t="n">
-        <v>3600</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2.52572</v>
+        <v>2.5257</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>2.49476</v>
+        <v>2.4948</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>2.3578</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2.02295</v>
+        <v>2.023</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1.47895</v>
+        <v>1.4711</v>
       </c>
     </row>
     <row r="4" ht="14.1" customHeight="1" s="4">
       <c r="A4" s="1" t="n">
-        <v>5400</v>
+        <v>1.5</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>2.38605</v>
+        <v>2.3861</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2.32562</v>
+        <v>2.3256</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>2.1344</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1.80201</v>
+        <v>1.802</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1.35385</v>
+        <v>1.3476</v>
       </c>
     </row>
     <row r="5" ht="14.1" customHeight="1" s="4">
       <c r="A5" s="1" t="n">
-        <v>7200</v>
+        <v>2</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2.17085</v>
+        <v>2.1708</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2.10842</v>
+        <v>2.1084</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1.92362</v>
+        <v>1.9236</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1.62594</v>
+        <v>1.6259</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.23659</v>
+        <v>1.2311</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>9000</v>
+        <v>2.5</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1.95664</v>
+        <v>1.9566</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1.90059</v>
+        <v>1.9006</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1.73598</v>
+        <v>1.736</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.47198</v>
+        <v>1.472</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1.12167</v>
+        <v>1.1167</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>10800</v>
+        <v>3</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1.76618</v>
+        <v>1.7662</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1.71653</v>
+        <v>1.7165</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>1.5702</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.33326</v>
+        <v>1.3333</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1.01278</v>
+        <v>1.0081</v>
       </c>
     </row>
   </sheetData>
